--- a/extenbooks/ES1202.xlsx
+++ b/extenbooks/ES1202.xlsx
@@ -1081,11 +1081,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_assembly</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1202 — NSW/EC (ST 2002) — PENDING</t>
+          <t># ES1202 — NSW/EC (Shaikh &amp; Tonak 2002)</t>
         </is>
       </c>
     </row>
@@ -1257,87 +1257,43 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: validated_book_and_extension.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S607-COMBINED / NIPA T20100 compensation. 74 rows 1952-2025. 1952=-4.73%, 1997=-2.03%. Range [-6.43%, +15.63%]. Normalizing by labor compensation rather than GDP gives larger swings (since NSW changes faster than wages over the period).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>needs EC</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>S607 / EC (BEA NIPA Table 2.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1202.xlsx
+++ b/extenbooks/ES1202.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 3</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–1997</t>
+          <t>1952-2025</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1234,54 +1234,63 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1202-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shaikh &amp; Tonak 2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1202 — NSW/EC (Shaikh &amp; Tonak 2002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1202 — NSW/EC (Shaikh &amp; Tonak 2002)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S607-COMBINED / NIPA T20100 compensation. 74 rows 1952-2025. 1952=-4.73%, 1997=-2.03%. Range [-6.43%, +15.63%]. Normalizing by labor compensation rather than GDP gives larger swings (since NSW changes faster than wages over the period).</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>S607-COMBINED / NIPA T20100 compensation. 74 rows 1952-2025. 1952=-4.73%, 1997=-2.03%. Range [-6.43%, +15.63%]. Normalizing by labor compensation rather than GDP gives larger swings (since NSW changes faster than wages over the period).</t>
         </is>
       </c>
     </row>
@@ -1292,6 +1301,18 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1308,10 +1329,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1336,235 +1357,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NSW/EC expresses the net social wage as a fraction of total employee compensation (EC). EC is the total cost to capitalists of hiring workers: wages + salaries + employer contributions for social insurance + other labor income. This is the authors' preferred normalization because EC is the most economically meaningful denominator for assessing redistribution — it measures the net social wage relative to the direct labor income relationship between workers and capital. NSW/GDP (ES1201) uses economy size; NSW/EC uses the labor income base.</t>
+          <t>VERBATIM (Moos 2017, Section 2 'Net Social Wage Methodology', transcription line 84): "The net social wage estimates, as developed by Shaikh and Tonak (1987), show if there has been a net transfer from capital to workers, vis-a-vis the state, or if workers have self-financed the benefits they receive. The net social wage (NSW) is calculated by adding up all of the fiscal transfers that workers have received from public expenditures, minus what they pay in taxes." Defines the NSW numerator that, divided by EC, yields ES1202.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_2002, p.249-250; full_transcription.md FORMULAS AND DEFINITIONS and Comparison with Employee Compensation sections</t>
+          <t>EXTERNAL: Moos, Katherine A. 2017. 'Neoliberal Redistributive Policy: The U.S. Net Social Wage in the 21st Century.' UMass Amherst Working Paper 2017-18, Section 2, pp.3-4. Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2017_Moos_NSW_21st_Century/full_transcription.md line 84.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The central finding of Shaikh &amp; Tonak (2002): over the full postwar period 1952-1997, the average NSW/EC ratio is 0.6% — effectively zero. The ratio seldom fluctuates beyond +/-4% of EC (Figure 29.3). This confirms that social wage flows largely recirculate income among wage and salary earners; the welfare state has very limited redistributive impact on worker incomes when taxes are properly accounted for.</t>
+          <t>VERBATIM (Moos 2017, Section 4, transcription line 150): "In Figure 2, we can see that after 1970, the NSW as a ratio of employee compensation was positive. It is compelling that U.S. fiscal policy appears to be more redistributive towards labor during the neoliberal era, especially in the 21st century." External authority that the NSW/EC ratio (the ES1202 quantity) turned persistently positive after 1970, contradicting the original ST 2002 finding of near-zero average across 1952-1997.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_2002, pp.253-255 Fig 29.3; full_transcription.md FIGURE 29.3 and FINAL SUMMARY sections</t>
+          <t>EXTERNAL: Moos 2017, Section 4 'The Net Social Wage in the 21st Century', p.6. Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2017_Moos_NSW_21st_Century/full_transcription.md line 150.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>phase_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Figure 29.3 shows three phases clearly. Boom (1952-1969): NSW/EC mostly negative, -2% to -7%; true real wage below apparent real wage (Fig 29.4). Crisis (1969-1975): sharp rise to peak ~+9% around 1975. Reagan-Bush attack (1975-1989): dramatic secular decline in base NSW, returns to negative even at peak unemployment (1982-83). Clinton era (1989-1997): modest recovery to near zero; benefit ratio does not fall when unemployment falls (evidence of raised noncyclical base); by 1997 NSW/EC essentially zero.</t>
+          <t>VERBATIM (Moos 2017 methodology extract, MOOS_2017_NSW_METHODOLOGY_EXTRACTED.md Table 2): "NSW/EC | -0.022 | 0.024 | 0.037 | 0.161" (min | median | mean | max for U.S. NSW Data 1959-2012). Direct external benchmark for ES1202 extended-series validation: V11 should target mean NSW/EC ~ 0.037 and max ~ 0.161 (2010) when extension covers 1959-2012, rather than the ST 2002 mean of 0.006 which is for 1952-1997.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_2002, pp.251-254; full_transcription.md FIGURE 29.3 section and HISTORICAL PHASES SUMMARY</t>
+          <t>EXTERNAL: Moos 2017, Table 2 'Summary Statistics of U.S. NSW Data, 1959-2012', p.8. Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/[2025.10.02] MOOS_2017_NSW_METHODOLOGY_EXTRACTED.md (Table 2 section).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ES1202 = NSW / EC, where NSW = (E1-T1) + (E2-T2)*LS and EC = total employee compensation from NIPA. The True Real Wage per FEE = (EC + NSW)/(CPI * FEE). The Apparent Real Wage per FEE = EC/(CPI * FEE). The gap between True and Apparent Real Wage equals the net social wage divided by FEE*CPI. Negative NSW means true real wage &lt; apparent real wage.</t>
+          <t>the net social wage as a percentage of employee compensation is very modest indeed: It seldom fluctuates beyond ±4 percent ... Its average is a mere 0.6 percent (Figure 29.3, p. 253)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_2002, p.250; full_transcription.md SUMMARY OF KEY FORMULAS section</t>
+          <t>Shaikh &amp; Tonak 2002, Principal Findings, p.248</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>benchmark_value</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Figure 29.3 data points (NSW/EC ratio): 1952 approx -4% to -6%; 1964 approx -1.7% (Table 29.1: NSW=-3.49bn, EC=209.37bn → -1.67%); 1975 peak approx +9%; 1980: NSW=79.83bn (from appendix key data); 1989: NSW=-63.63bn; 1997: approx 0%. Real wages (1982 dollars, per FEE): 1952 apparent=$13,748 true=$12,941 (gap=-$807); 1980 apparent=$24,264 true=$23,714 (gap=-$550); 1997 apparent=$24,532 true=$24,823 (gap=+$291, NSW finally positive).</t>
+          <t>Year-to-year movements of the net social wage are strongly affected by the level of unemployment, since this affects: Government expenditures on welfare, unemployment insurance, and so on; The taxes paid by workers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ST_2002, Table 29.1; Appendix; full_transcription.md KEY DATA POINTS FROM APPENDIX section</t>
+          <t>Shaikh &amp; Tonak 2002, Cyclical Variations, p.248</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EC data from BEA NIPA: wages + salaries + employer social insurance contributions + other labor income. Same annual NIPA source as NSW components. 1952-1997 coverage. Labor share LS = wages and salaries / total personal income (ranges 0.69-0.73). Full-time equivalent employees (FEE) from BLS for per-worker calculations.</t>
+          <t>the long boom of 1947-1968 gave way to a subsequent long phase of slowdown and stagnation from 1969 to 1989, the resulting rise in structural unemployment in the latter phase triggered: Automatic rises in government spending; Simultaneous declines in tax revenues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_2002, pp.249-250, Appendix pp.258-265; full_transcription.md DATA SOURCES section</t>
+          <t>Shaikh &amp; Tonak 2002, U.S. Example, p.248</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Figure 29.2: Labor benefit and tax ratios (benefits/EC and taxes/EC) plotted alongside unemployment rate. Benefits ratio starts ~12% in 1952, rises to ~25-33% by peak; tax ratio starts ~12%, rises steadily. By 1997 benefit and tax ratios are virtually identical (~31-32% each), explaining the near-zero NSW/EC. Figure 29.3 is the primary plot for ES1202 — NET social wage ratio fluctuating around zero. Figure 29.4 uses NSW/EC to compute true real wage vs apparent real wage.</t>
+          <t>NSW/EC expresses the net social wage as a fraction of total employee compensation (EC). EC is the total cost to capitalists of hiring workers: wages + salaries + employer contributions for social insurance + other labor income. This is the authors' preferred normalization because EC is the most economically meaningful denominator for assessing redistribution — it measures the net social wage relative to the direct labor income relationship between workers and capital. NSW/GDP (ES1201) uses economy size; NSW/EC uses the labor income base.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ST_2002, pp.252-253; full_transcription.md FIGURE 29.2 and FIGURE 29.3 sections</t>
+          <t>ST_2002, p.249-250; full_transcription.md FORMULAS AND DEFINITIONS and Comparison with Employee Compensation sections</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>policy_interpretation</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The near-zero long-run NSW/EC is the paper's central policy conclusion: the welfare state is not a net provider to workers; workers essentially pay for their own social programs. The primary basis of workers' standard of living remains the wage won from employers, not state redistribution. Class struggle and the reserve army of labor remain central determinants. The Reagan-Bush era broke historical precedent by making NSW negative during high unemployment (1982-83), with labor paying a net tax that partly offset expanded defense spending.</t>
+          <t>The central finding of Shaikh &amp; Tonak (2002): over the full postwar period 1952-1997, the average NSW/EC ratio is 0.6% — effectively zero. The ratio seldom fluctuates beyond +/-4% of EC (Figure 29.3). This confirms that social wage flows largely recirculate income among wage and salary earners; the welfare state has very limited redistributive impact on worker incomes when taxes are properly accounted for.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ST_2002, pp.254-256 Summary and Conclusions; full_transcription.md POLICY AND THEORETICAL IMPLICATIONS section</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>ST_2002, pp.253-255 Fig 29.3; full_transcription.md FIGURE 29.3 and FINAL SUMMARY sections</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>phase_description</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Figure 29.3 shows three phases clearly. Boom (1952-1969): NSW/EC mostly negative, -2% to -7%; true real wage below apparent real wage (Fig 29.4). Crisis (1969-1975): sharp rise to peak ~+9% around 1975. Reagan-Bush attack (1975-1989): dramatic secular decline in base NSW, returns to negative even at peak unemployment (1982-83). Clinton era (1989-1997): modest recovery to near zero; benefit ratio does not fall when unemployment falls (evidence of raised noncyclical base); by 1997 NSW/EC essentially zero.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_2002, pp.251-254; full_transcription.md FIGURE 29.3 section and HISTORICAL PHASES SUMMARY</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NSW/EC ratio from Shaikh &amp; Tonak (2002), covering 1952-1997. Primary measure in the paper (Figure 29.3). Average 0.6% over 45 years — effectively zero. Fluctuates within +/-4% to +/-9% driven by unemployment. True real wage = apparent real wage + NSW/FEE adjusted for CPI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>ES1202 = NSW / EC, where NSW = (E1-T1) + (E2-T2)*LS and EC = total employee compensation from NIPA. The True Real Wage per FEE = (EC + NSW)/(CPI * FEE). The Apparent Real Wage per FEE = EC/(CPI * FEE). The gap between True and Apparent Real Wage equals the net social wage divided by FEE*CPI. Negative NSW means true real wage &lt; apparent real wage.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_2002, p.250; full_transcription.md SUMMARY OF KEY FORMULAS section</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>benchmark_value</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Figure 29.3 data points (NSW/EC ratio): 1952 approx -4% to -6%; 1964 approx -1.7% (Table 29.1: NSW=-3.49bn, EC=209.37bn → -1.67%); 1975 peak approx +9%; 1980: NSW=79.83bn (from appendix key data); 1989: NSW=-63.63bn; 1997: approx 0%. Real wages (1982 dollars, per FEE): 1952 apparent=$13,748 true=$12,941 (gap=-$807); 1980 apparent=$24,264 true=$23,714 (gap=-$550); 1997 apparent=$24,532 true=$24,823 (gap=+$291, NSW finally positive).</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_2002, Table 29.1; Appendix; full_transcription.md KEY DATA POINTS FROM APPENDIX section</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EC data from BEA NIPA: wages + salaries + employer social insurance contributions + other labor income. Same annual NIPA source as NSW components. 1952-1997 coverage. Labor share LS = wages and salaries / total personal income (ranges 0.69-0.73). Full-time equivalent employees (FEE) from BLS for per-worker calculations.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST_2002, pp.249-250, Appendix pp.258-265; full_transcription.md DATA SOURCES section</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NIPA revision effects: Moos (2017) replication shows slightly higher values in overlap period due to post-1999 comprehensive NIPA revision</t>
+          <t>Figure 29.2: Labor benefit and tax ratios (benefits/EC and taxes/EC) plotted alongside unemployment rate. Benefits ratio starts ~12% in 1952, rises to ~25-33% by peak; tax ratio starts ~12%, rises steadily. By 1997 benefit and tax ratios are virtually identical (~31-32% each), explaining the near-zero NSW/EC. Figure 29.3 is the primary plot for ES1202 — NET social wage ratio fluctuating around zero. Figure 29.4 uses NSW/EC to compute true real wage vs apparent real wage.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST_2002, pp.252-253; full_transcription.md FIGURE 29.2 and FIGURE 29.3 sections</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>policy_interpretation</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EC denominator includes employer Social Security contributions, making this ratio slightly different from wage-only normalizations</t>
+          <t>The near-zero long-run NSW/EC is the paper's central policy conclusion: the welfare state is not a net provider to workers; workers essentially pay for their own social programs. The primary basis of workers' standard of living remains the wage won from employers, not state redistribution. Class struggle and the reserve army of labor remain central determinants. The Reagan-Bush era broke historical precedent by making NSW negative during high unemployment (1982-83), with labor paying a net tax that partly offset expanded defense spending.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ST_2002, pp.254-256 Summary and Conclusions; full_transcription.md POLICY AND THEORETICAL IMPLICATIONS section</t>
         </is>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1201</t>
-        </is>
-      </c>
+          <t>the net social wage as a percentage of employee compensation is very modest indeed: It seldom fluctuates beyond ±4 percent ... Its average is a mere 0.6 percent (Figure 29.3, p. 253)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S607</t>
-        </is>
-      </c>
+          <t>Year-to-year movements of the net social wage are strongly affected by the level of unemployment, since this affects: Government expenditures on welfare, unemployment insurance, and so on; The taxes paid by workers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ES1302</t>
-        </is>
-      </c>
+          <t>the long boom of 1947-1968 gave way to a subsequent long phase of slowdown and stagnation from 1969 to 1989, the resulting rise in structural unemployment in the latter phase triggered: Automatic rises in government spending; Simultaneous declines in tax revenues</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ST_2002</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism, ed. Boushey, Baiman, and Saunders. M.E. Sharpe, Armonk. pp. 247-265.</t>
-        </is>
-      </c>
-    </row>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NSW/EC ratio from Shaikh &amp; Tonak (2002), covering 1952-1997. Primary measure in the paper (Figure 29.3). Average 0.6% over 45 years — effectively zero. Fluctuates within +/-4% to +/-9% driven by unemployment. True real wage = apparent real wage + NSW/FEE adjusted for CPI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NIPA revision effects: Moos (2017) replication shows slightly higher values in overlap period due to post-1999 comprehensive NIPA revision</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EC denominator includes employer Social Security contributions, making this ratio slightly different from wage-only normalizations</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ES1201</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ES1302</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ST_2002</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism, ed. Boushey, Baiman, and Saunders. M.E. Sharpe, Armonk. pp. 247-265.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. Survey of Current Business, various years.</t>
         </is>
@@ -1581,11 +1741,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1652,7 +1812,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1833,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1964": -0.0167, "1975": 0.09, "1997": 0.006, "2010": 0.161}</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1857,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
